--- a/Team-Data/2012-13/1-12-2012-13.xlsx
+++ b/Team-Data/2012-13/1-12-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
         <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>0.583</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>37.1</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
         <v>81.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
         <v>8.9</v>
@@ -691,76 +758,76 @@
         <v>23.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
         <v>13.4</v>
       </c>
       <c r="P2" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.702</v>
+        <v>0.705</v>
       </c>
       <c r="R2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>30.9</v>
       </c>
       <c r="T2" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
         <v>23.2</v>
       </c>
       <c r="V2" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W2" t="n">
         <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
         <v>17.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG2" t="n">
         <v>9</v>
       </c>
       <c r="AH2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI2" t="n">
         <v>11</v>
       </c>
-      <c r="AI2" t="n">
-        <v>14</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
@@ -784,7 +851,7 @@
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
         <v>24</v>
@@ -799,22 +866,22 @@
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -981,16 +1048,16 @@
         <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>10</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
@@ -1124,28 +1191,28 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
       </c>
       <c r="AM4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
         <v>25</v>
@@ -1157,7 +1224,7 @@
         <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
@@ -1172,13 +1239,13 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>0.25</v>
+        <v>0.257</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
@@ -1225,37 +1292,37 @@
         <v>35.2</v>
       </c>
       <c r="J5" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O5" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="P5" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
         <v>29.7</v>
       </c>
       <c r="T5" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U5" t="n">
         <v>19.4</v>
@@ -1264,7 +1331,7 @@
         <v>14.2</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X5" t="n">
         <v>6.4</v>
@@ -1273,25 +1340,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA5" t="n">
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.5</v>
+        <v>95.7</v>
       </c>
       <c r="AC5" t="n">
         <v>-8.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>28</v>
       </c>
       <c r="AF5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG5" t="n">
         <v>28</v>
@@ -1312,7 +1379,7 @@
         <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN5" t="n">
         <v>20</v>
@@ -1321,19 +1388,19 @@
         <v>3</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU5" t="n">
         <v>29</v>
@@ -1342,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -1389,70 +1456,70 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.571</v>
+        <v>0.588</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.442</v>
       </c>
       <c r="L6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="M6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
-        <v>0.358</v>
+        <v>0.363</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.79</v>
+        <v>0.792</v>
       </c>
       <c r="R6" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
         <v>43.2</v>
       </c>
       <c r="U6" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V6" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Z6" t="n">
         <v>19.4</v>
@@ -1461,28 +1528,28 @@
         <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1503,37 +1570,37 @@
         <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
         <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1661,7 +1728,7 @@
         <v>29</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>27</v>
@@ -1676,7 +1743,7 @@
         <v>10</v>
       </c>
       <c r="AM7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN7" t="n">
         <v>13</v>
@@ -1691,13 +1758,13 @@
         <v>22</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
         <v>30</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -1753,67 +1820,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.395</v>
+        <v>0.378</v>
       </c>
       <c r="H8" t="n">
         <v>49.2</v>
       </c>
       <c r="I8" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J8" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L8" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
         <v>19.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.358</v>
+        <v>0.351</v>
       </c>
       <c r="O8" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P8" t="n">
         <v>21.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.789</v>
+        <v>0.791</v>
       </c>
       <c r="R8" t="n">
         <v>9.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T8" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U8" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="V8" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W8" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y8" t="n">
         <v>4.7</v>
@@ -1822,25 +1889,25 @@
         <v>21.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>99.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>-3.7</v>
+        <v>-4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF8" t="n">
         <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -1858,10 +1925,10 @@
         <v>14</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1876,31 +1943,31 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV8" t="n">
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2080,19 @@
         <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2046,10 +2113,10 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>30</v>
@@ -2058,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>1</v>
@@ -2073,7 +2140,7 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY9" t="n">
         <v>28</v>
@@ -2085,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>0.368</v>
+        <v>0.378</v>
       </c>
       <c r="H10" t="n">
         <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
-        <v>80.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L10" t="n">
         <v>6.3</v>
@@ -2150,37 +2217,37 @@
         <v>0.374</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P10" t="n">
         <v>23.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.714</v>
+        <v>0.716</v>
       </c>
       <c r="R10" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="S10" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T10" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
         <v>15.2</v>
       </c>
       <c r="W10" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X10" t="n">
         <v>5.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z10" t="n">
         <v>19.9</v>
@@ -2189,22 +2256,22 @@
         <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF10" t="n">
         <v>22</v>
       </c>
-      <c r="AF10" t="n">
-        <v>24</v>
-      </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
         <v>8</v>
@@ -2213,22 +2280,22 @@
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
       </c>
       <c r="AM10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN10" t="n">
         <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2237,13 +2304,13 @@
         <v>26</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
         <v>25</v>
@@ -2255,19 +2322,19 @@
         <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
         <v>22</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
         <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -2392,13 +2459,13 @@
         <v>10</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2410,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
         <v>17</v>
@@ -2428,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.553</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,28 +2566,28 @@
         <v>38.2</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.459</v>
       </c>
       <c r="L12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="M12" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="O12" t="n">
         <v>19.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R12" t="n">
         <v>10.6</v>
@@ -2541,7 +2608,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>6.3</v>
@@ -2553,22 +2620,22 @@
         <v>19.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.4</v>
+        <v>105.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
         <v>10</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2577,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK12" t="n">
         <v>7</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>4</v>
@@ -2601,7 +2668,7 @@
         <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
         <v>7</v>
@@ -2619,7 +2686,7 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -2663,49 +2730,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.622</v>
+        <v>0.611</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81</v>
+        <v>80.8</v>
       </c>
       <c r="K13" t="n">
         <v>0.42</v>
       </c>
       <c r="L13" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M13" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O13" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="P13" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="R13" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
         <v>33.3</v>
@@ -2714,37 +2781,37 @@
         <v>46.3</v>
       </c>
       <c r="U13" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V13" t="n">
         <v>15.1</v>
       </c>
       <c r="W13" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X13" t="n">
         <v>6.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z13" t="n">
         <v>19.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>91.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
         <v>10</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2753,22 +2820,22 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
       </c>
       <c r="AL13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM13" t="n">
         <v>18</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>17</v>
       </c>
       <c r="AN13" t="n">
         <v>25</v>
@@ -2777,13 +2844,13 @@
         <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS13" t="n">
         <v>2</v>
@@ -2795,28 +2862,28 @@
         <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY13" t="n">
         <v>21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -2845,82 +2912,82 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
         <v>28</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.757</v>
+        <v>0.778</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J14" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.477</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
         <v>20.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O14" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.713</v>
+        <v>0.711</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T14" t="n">
-        <v>41.8</v>
+        <v>42</v>
       </c>
       <c r="U14" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="X14" t="n">
         <v>6.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="AB14" t="n">
         <v>101.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
         <v>10</v>
@@ -2929,19 +2996,19 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
         <v>4</v>
@@ -2956,28 +3023,28 @@
         <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>27</v>
       </c>
       <c r="AR14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS14" t="n">
         <v>17</v>
       </c>
-      <c r="AS14" t="n">
-        <v>19</v>
-      </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2986,16 +3053,16 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -3105,22 +3172,22 @@
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF15" t="n">
         <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>16</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3156,7 +3223,7 @@
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV15" t="n">
         <v>25</v>
@@ -3165,10 +3232,10 @@
         <v>19</v>
       </c>
       <c r="AX15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>11</v>
@@ -3180,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -3209,34 +3276,34 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
         <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J16" t="n">
         <v>82.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="L16" t="n">
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="N16" t="n">
         <v>0.348</v>
@@ -3245,49 +3312,49 @@
         <v>17.1</v>
       </c>
       <c r="P16" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.799</v>
+        <v>0.805</v>
       </c>
       <c r="R16" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S16" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U16" t="n">
         <v>21.1</v>
       </c>
       <c r="V16" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y16" t="n">
         <v>5.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
         <v>20.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3308,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,13 +3384,13 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3332,7 +3399,7 @@
         <v>3</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>13</v>
@@ -3341,7 +3408,7 @@
         <v>21</v>
       </c>
       <c r="AV16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3350,19 +3417,19 @@
         <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
         <v>13</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -3391,70 +3458,70 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.2</v>
+        <v>38</v>
       </c>
       <c r="J17" t="n">
-        <v>78.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K17" t="n">
-        <v>0.489</v>
+        <v>0.487</v>
       </c>
       <c r="L17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="M17" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.395</v>
+        <v>0.392</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P17" t="n">
         <v>22.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="R17" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="S17" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T17" t="n">
         <v>39.1</v>
       </c>
       <c r="U17" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="V17" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W17" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
         <v>19</v>
@@ -3463,28 +3530,28 @@
         <v>19.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.6</v>
+        <v>101.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF17" t="n">
         <v>4</v>
       </c>
-      <c r="AF17" t="n">
-        <v>3</v>
-      </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
         <v>13</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,22 +3560,22 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,16 +3587,16 @@
         <v>29</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3541,11 +3608,11 @@
         <v>14</v>
       </c>
       <c r="BB17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC17" t="n">
         <v>5</v>
       </c>
-      <c r="BC17" t="n">
-        <v>4</v>
-      </c>
       <c r="BD17" t="n">
         <v>10</v>
       </c>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -3666,7 +3733,7 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3687,7 +3754,7 @@
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3702,7 +3769,7 @@
         <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-0.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3860,16 +3927,16 @@
         <v>27</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4027,16 +4094,16 @@
         <v>27</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>15</v>
@@ -4060,7 +4127,7 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
@@ -4078,7 +4145,7 @@
         <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
         <v>16</v>
@@ -4090,7 +4157,7 @@
         <v>28</v>
       </c>
       <c r="BC20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>4.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF21" t="n">
         <v>7</v>
@@ -4212,13 +4279,13 @@
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ21" t="n">
         <v>6</v>
       </c>
       <c r="AK21" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4245,7 +4312,7 @@
         <v>26</v>
       </c>
       <c r="AT21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4430,7 +4497,7 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
         <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>0.361</v>
+        <v>0.343</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
@@ -4501,22 +4568,22 @@
         <v>37.8</v>
       </c>
       <c r="J23" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O23" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="P23" t="n">
         <v>16.4</v>
@@ -4528,49 +4595,49 @@
         <v>10.4</v>
       </c>
       <c r="S23" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T23" t="n">
         <v>42.9</v>
       </c>
       <c r="U23" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W23" t="n">
         <v>5.8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA23" t="n">
         <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF23" t="n">
         <v>22</v>
       </c>
       <c r="AG23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
@@ -4582,16 +4649,16 @@
         <v>14</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>19</v>
       </c>
       <c r="AN23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
         <v>29</v>
@@ -4612,10 +4679,10 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4624,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
         <v>15</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -4665,58 +4732,58 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.421</v>
+        <v>0.405</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J24" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L24" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M24" t="n">
         <v>18.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O24" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="P24" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S24" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T24" t="n">
         <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V24" t="n">
         <v>12.8</v>
@@ -4728,7 +4795,7 @@
         <v>5.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
         <v>18.9</v>
@@ -4737,22 +4804,22 @@
         <v>17</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.2</v>
+        <v>-4.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4764,13 +4831,13 @@
         <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
         <v>12</v>
@@ -4788,25 +4855,25 @@
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT24" t="n">
         <v>22</v>
       </c>
       <c r="AU24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV24" t="n">
         <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4818,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
         <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.333</v>
+        <v>0.316</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
@@ -4865,25 +4932,25 @@
         <v>37.6</v>
       </c>
       <c r="J25" t="n">
-        <v>84.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L25" t="n">
         <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="O25" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="P25" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0.745</v>
@@ -4892,28 +4959,28 @@
         <v>11.4</v>
       </c>
       <c r="S25" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T25" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V25" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W25" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y25" t="n">
         <v>5.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA25" t="n">
         <v>18.2</v>
@@ -4922,13 +4989,13 @@
         <v>95.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.2</v>
+        <v>-4.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF25" t="n">
         <v>27</v>
@@ -4952,7 +5019,7 @@
         <v>24</v>
       </c>
       <c r="AM25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN25" t="n">
         <v>27</v>
@@ -4967,16 +5034,16 @@
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
         <v>28</v>
       </c>
       <c r="AT25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
         <v>5</v>
@@ -4985,10 +5052,10 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ25" t="n">
         <v>21</v>
@@ -4997,10 +5064,10 @@
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>13</v>
@@ -5116,7 +5183,7 @@
         <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
@@ -5131,7 +5198,7 @@
         <v>24</v>
       </c>
       <c r="AL26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
@@ -5152,19 +5219,19 @@
         <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT26" t="n">
         <v>20</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV26" t="n">
         <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX26" t="n">
         <v>21</v>
@@ -5176,7 +5243,7 @@
         <v>5</v>
       </c>
       <c r="BA26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
         <v>12</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
         <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.351</v>
+        <v>0.361</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,10 +5296,10 @@
         <v>36.5</v>
       </c>
       <c r="J27" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L27" t="n">
         <v>6.8</v>
@@ -5241,52 +5308,52 @@
         <v>19.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
       <c r="O27" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P27" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q27" t="n">
         <v>0.768</v>
       </c>
       <c r="R27" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S27" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="T27" t="n">
         <v>40.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Z27" t="n">
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.2</v>
+        <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
         <v>10</v>
@@ -5295,19 +5362,19 @@
         <v>24</v>
       </c>
       <c r="AF27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG27" t="n">
         <v>24</v>
       </c>
-      <c r="AG27" t="n">
-        <v>25</v>
-      </c>
       <c r="AH27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
         <v>21</v>
@@ -5319,22 +5386,22 @@
         <v>16</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP27" t="n">
         <v>14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT27" t="n">
         <v>25</v>
@@ -5343,19 +5410,19 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW27" t="n">
         <v>12</v>
       </c>
-      <c r="AW27" t="n">
-        <v>13</v>
-      </c>
       <c r="AX27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>24</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>25</v>
       </c>
       <c r="BA27" t="n">
         <v>16</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5544,7 @@
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="n">
         <v>3</v>
@@ -5504,7 +5571,7 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
         <v>21</v>
@@ -5531,7 +5598,7 @@
         <v>4</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="n">
         <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
@@ -5671,7 +5738,7 @@
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
@@ -5686,7 +5753,7 @@
         <v>23</v>
       </c>
       <c r="AO29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5695,7 +5762,7 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
         <v>26</v>
@@ -5713,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>18</v>
@@ -5725,7 +5792,7 @@
         <v>21</v>
       </c>
       <c r="BB29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" t="n">
         <v>19</v>
       </c>
       <c r="G30" t="n">
-        <v>0.513</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
@@ -5775,49 +5842,49 @@
         <v>36.5</v>
       </c>
       <c r="J30" t="n">
-        <v>81.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L30" t="n">
         <v>6.5</v>
       </c>
       <c r="M30" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O30" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="P30" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R30" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>42.4</v>
+        <v>42.7</v>
       </c>
       <c r="U30" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y30" t="n">
         <v>6.2</v>
@@ -5829,16 +5896,16 @@
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.3</v>
+        <v>98.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5850,16 +5917,16 @@
         <v>20</v>
       </c>
       <c r="AI30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM30" t="n">
         <v>25</v>
@@ -5868,19 +5935,19 @@
         <v>9</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
@@ -5889,7 +5956,7 @@
         <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
@@ -5939,58 +6006,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.176</v>
+        <v>0.152</v>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I31" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="J31" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.409</v>
+        <v>0.408</v>
       </c>
       <c r="L31" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="O31" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="P31" t="n">
         <v>19.8</v>
       </c>
-      <c r="N31" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="O31" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="P31" t="n">
-        <v>20</v>
-      </c>
       <c r="Q31" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="R31" t="n">
         <v>11.4</v>
       </c>
       <c r="S31" t="n">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
       <c r="T31" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="U31" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V31" t="n">
         <v>15.2</v>
@@ -5999,22 +6066,22 @@
         <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
         <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
         <v>19</v>
       </c>
       <c r="AB31" t="n">
-        <v>89.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-8</v>
       </c>
       <c r="AD31" t="n">
         <v>29</v>
@@ -6041,10 +6108,10 @@
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN31" t="n">
         <v>29</v>
@@ -6059,28 +6126,28 @@
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV31" t="n">
         <v>23</v>
       </c>
       <c r="AW31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
         <v>22</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-12-2012-13</t>
+          <t>2013-01-12</t>
         </is>
       </c>
     </row>
